--- a/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.415563718989383</v>
+        <v>1.415563718989385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3653792945421858</v>
+        <v>0.365379294542185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.699433460990047</v>
+        <v>0.6994334609900499</v>
       </c>
       <c r="E2" t="n">
         <v>2.13169397698872</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001069620034727781</v>
+        <v>0.0001069620034727728</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01406648442462934</v>
+        <v>0.01406648442462925</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06948450970190394</v>
+        <v>0.06948450970190397</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1221206520745263</v>
+        <v>-0.1221206520745265</v>
       </c>
       <c r="E3" t="n">
         <v>0.150253620923785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8395723070577604</v>
+        <v>0.8395723070577614</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1520,13 +1520,13 @@
         <v>0.1561342593458452</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1125799052845432</v>
+        <v>-0.1125799052845433</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4994551448568427</v>
+        <v>0.4994551448568428</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2153756879251694</v>
+        <v>0.2153756879251695</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08228016691387022</v>
+        <v>0.08228016691387016</v>
       </c>
       <c r="C5" t="n">
         <v>0.1200746414081911</v>
@@ -1551,7 +1551,7 @@
         <v>0.3176221395304866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4931913324621541</v>
+        <v>0.4931913324621544</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1567,16 +1567,16 @@
         <v>0.2682770111457028</v>
       </c>
       <c r="C6" t="n">
-        <v>0.130013240084899</v>
+        <v>0.1300132400848991</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01345574306594155</v>
+        <v>0.01345574306594133</v>
       </c>
       <c r="E6" t="n">
-        <v>0.523098279225464</v>
+        <v>0.5230982792254644</v>
       </c>
       <c r="F6" t="n">
-        <v>0.039069024183887</v>
+        <v>0.03906902418388717</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05866897476675003</v>
+        <v>0.05866897476675006</v>
       </c>
       <c r="C7" t="n">
         <v>0.138655478374334</v>
@@ -1601,7 +1601,7 @@
         <v>0.330428718639617</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6722020875369368</v>
+        <v>0.6722020875369367</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06280541537249595</v>
+        <v>0.06280541537249594</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1473120129983398</v>
+        <v>0.1473120129983399</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2259208245943463</v>
+        <v>-0.2259208245943466</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3515316553393382</v>
+        <v>0.3515316553393385</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6698580785094372</v>
+        <v>0.6698580785094375</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1645,13 +1645,13 @@
         <v>0.120288228326492</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09673745679397036</v>
+        <v>-0.09673745679397053</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3747837337741395</v>
+        <v>0.3747837337741398</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2477833667498957</v>
+        <v>0.2477833667498961</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02793986317350432</v>
+        <v>0.02793986317350415</v>
       </c>
       <c r="C10" t="n">
         <v>0.1999310656891016</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3639178249678465</v>
+        <v>-0.3639178249678467</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4197975513148551</v>
+        <v>0.419797551314855</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8888595085924254</v>
+        <v>0.888859508592426</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07356614672567929</v>
+        <v>-0.07356614672567961</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2061356399317544</v>
+        <v>0.2061356399317545</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4775845769220345</v>
+        <v>-0.477584576922035</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3304522834706759</v>
+        <v>0.3304522834706757</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7211799737560187</v>
+        <v>0.7211799737560176</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03199774539716499</v>
+        <v>0.03199774539716469</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2061594449032441</v>
+        <v>0.2061594449032442</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.372067341685963</v>
+        <v>-0.3720673416859635</v>
       </c>
       <c r="E12" t="n">
-        <v>0.436062832480293</v>
+        <v>0.4360628324802929</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8766567670029284</v>
+        <v>0.8766567670029295</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.006374277414136445</v>
+        <v>-0.006374277414136828</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1965463686430545</v>
+        <v>0.1965463686430544</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3915980812466558</v>
+        <v>-0.391598081246656</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3788495264183829</v>
+        <v>0.3788495264183824</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9741280078152985</v>
+        <v>0.974128007815297</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2378369521738852</v>
+        <v>-0.2378369521738856</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2077401681853178</v>
+        <v>0.2077401681853177</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6450001999594017</v>
+        <v>-0.6450001999594019</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1693262956116314</v>
+        <v>0.1693262956116307</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2522600895661904</v>
+        <v>0.2522600895661893</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08511172439276481</v>
+        <v>-0.08511172439276508</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2148668528732516</v>
+        <v>0.2148668528732521</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5062430174958046</v>
+        <v>-0.5062430174958057</v>
       </c>
       <c r="E15" t="n">
-        <v>0.336019568710275</v>
+        <v>0.3360195687102756</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6920210823806994</v>
+        <v>0.692021082380699</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09645326976338156</v>
+        <v>0.09645326976338127</v>
       </c>
       <c r="C16" t="n">
         <v>0.1999648883531895</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2954707095814427</v>
+        <v>-0.2954707095814431</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4883772491082059</v>
+        <v>0.4883772491082056</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6295566025541415</v>
+        <v>0.6295566025541425</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2658960001519028</v>
+        <v>-0.2658960001519032</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1973633420962449</v>
+        <v>0.197363342096245</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6527210425290008</v>
+        <v>-0.6527210425290013</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1209290422251952</v>
+        <v>0.1209290422251949</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1779026046618571</v>
+        <v>0.1779026046618565</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1410581106617721</v>
+        <v>0.1410581106617718</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1862982201656765</v>
+        <v>0.1862982201656767</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2240796912468675</v>
+        <v>-0.2240796912468682</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5061959125704116</v>
+        <v>0.5061959125704119</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4489522418144455</v>
+        <v>0.4489522418144468</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08344985283767306</v>
+        <v>-0.08344985283767346</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2041354907480703</v>
+        <v>0.2041354907480704</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4835480626703003</v>
+        <v>-0.4835480626703009</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3166483569949541</v>
+        <v>0.3166483569949539</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6826890852425085</v>
+        <v>0.6826890852425073</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2678101521998021</v>
+        <v>-0.2678101521998024</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1911082668602465</v>
+        <v>0.1911082668602463</v>
       </c>
       <c r="D20" t="n">
         <v>-0.6423754723937547</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1067551679941506</v>
+        <v>0.10675516799415</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1611085253078226</v>
+        <v>0.1611085253078218</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2357850011436257</v>
+        <v>-0.2357850011436261</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1852596407770944</v>
+        <v>0.1852596407770945</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5988872248555588</v>
+        <v>-0.5988872248555595</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1273172225683073</v>
+        <v>0.1273172225683072</v>
       </c>
       <c r="F21" t="n">
-        <v>0.203114829079299</v>
+        <v>0.2031148290792987</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05887556586940961</v>
+        <v>0.05887556586940924</v>
       </c>
       <c r="C22" t="n">
         <v>0.1964795852898691</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3262173449960996</v>
+        <v>-0.3262173449961</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4439684767349188</v>
+        <v>0.4439684767349185</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7644423623312731</v>
+        <v>0.7644423623312745</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1370978385961138</v>
+        <v>-0.137097838596114</v>
       </c>
       <c r="C23" t="n">
-        <v>0.201594027127635</v>
+        <v>0.2015940271276349</v>
       </c>
       <c r="D23" t="n">
         <v>-0.532214871264669</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2580191940724414</v>
+        <v>0.2580191940724411</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4964608030112682</v>
+        <v>0.4964608030112675</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2020,13 +2020,13 @@
         <v>0.1025093436987393</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.06948455168514248</v>
+        <v>-0.06948455168514242</v>
       </c>
       <c r="E24" t="n">
         <v>0.3323446917715916</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1997978500285618</v>
+        <v>0.1997978500285615</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03463267714177365</v>
+        <v>0.03463267714177366</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08275182901981309</v>
+        <v>0.08275182901981308</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1275579273918765</v>
+        <v>-0.1275579273918764</v>
       </c>
       <c r="E25" t="n">
         <v>0.1968232816754238</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6755724289525702</v>
+        <v>0.67557242895257</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1488260434975333</v>
+        <v>-0.1488260434975335</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1041192044224461</v>
+        <v>0.104119204422446</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3528959342644912</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05524384726942458</v>
+        <v>0.05524384726942427</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1528946709271375</v>
+        <v>0.1528946709271366</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03169527812066084</v>
+        <v>-0.03169527812066093</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1100545842581242</v>
+        <v>0.1100545842581243</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.247398299600113</v>
+        <v>-0.2473982996001133</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1840077433587913</v>
+        <v>0.1840077433587915</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7733498139601129</v>
+        <v>0.7733498139601125</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,16 +2114,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1415579970155404</v>
+        <v>0.1415579970155403</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1155062953631743</v>
+        <v>0.1155062953631742</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.08483018188392713</v>
+        <v>-0.0848301818839271</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3679461759150079</v>
+        <v>0.3679461759150076</v>
       </c>
       <c r="F28" t="n">
         <v>0.2203704862681708</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02793447775400478</v>
+        <v>-0.02793447775400486</v>
       </c>
       <c r="C29" t="n">
         <v>0.1096742534746417</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2428920645956194</v>
+        <v>-0.2428920645956195</v>
       </c>
       <c r="E29" t="n">
         <v>0.1870231090876098</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7989516794020014</v>
+        <v>0.7989516794020008</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2582177129441011</v>
+        <v>0.2582177129441012</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0379034316634053</v>
+        <v>0.03790343166340591</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1839283519933516</v>
+        <v>0.1839283519933505</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3325070738948506</v>
+        <v>0.3325070738948519</v>
       </c>
       <c r="F30" t="n">
-        <v>9.590676754537563e-12</v>
+        <v>9.590676754544794e-12</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4698373208221375</v>
+        <v>0.06813476221211853</v>
       </c>
       <c r="C31" t="n">
-        <v>0.03332861578287737</v>
+        <v>0.07489655592157836</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4045144342331247</v>
+        <v>-0.07865978996026518</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5351602074111503</v>
+        <v>0.2149293143845022</v>
       </c>
       <c r="F31" t="n">
-        <v>3.956166429174619e-45</v>
+        <v>0.36297112811455</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.004135564358761956</v>
+        <v>0.001079790152347911</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00494118969612754</v>
+        <v>0.005978338076640147</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.005548989486428436</v>
+        <v>-0.01063753716527123</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01382011820395235</v>
+        <v>0.01279711746996706</v>
       </c>
       <c r="F32" t="n">
-        <v>0.402616618830528</v>
+        <v>0.8566681240955263</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001079790152347925</v>
+        <v>0.004135564358761948</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00597833807664017</v>
+        <v>0.004941189696127534</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01063753716527126</v>
+        <v>-0.005548989486428432</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01279711746996711</v>
+        <v>0.01382011820395233</v>
       </c>
       <c r="F33" t="n">
-        <v>0.856668124095525</v>
+        <v>0.4026166188305283</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01398274283089319</v>
+        <v>-0.01398274283089321</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0155897166522796</v>
+        <v>0.01558971665227964</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.04453802599854555</v>
+        <v>-0.04453802599854564</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01657254033675916</v>
+        <v>0.01657254033675923</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3697611220226221</v>
+        <v>0.3697611220226229</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.06813476221211859</v>
+        <v>0.00191588801380837</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07489655592157843</v>
+        <v>0.004864009007753421</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.07865978996026524</v>
+        <v>-0.007617394461866739</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2149293143845024</v>
+        <v>0.01144917048948348</v>
       </c>
       <c r="F35" t="n">
-        <v>0.36297112811455</v>
+        <v>0.6936617214919621</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001915888013808376</v>
+        <v>0.4698373208221375</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004864009007753431</v>
+        <v>0.0333286157828773</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.007617394461866752</v>
+        <v>0.4045144342331247</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0114491704894835</v>
+        <v>0.5351602074111502</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6936617214919618</v>
+        <v>3.956166429173207e-45</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802938</v>
+        <v>-2.680600179802939</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981325</v>
+        <v>0.4771933030981503</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768271168e-08</v>
+        <v>1.938181768273511e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,7 +2394,7 @@
         <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033997</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
         <v>0.79975540801217</v>
@@ -2410,10 +2410,10 @@
         <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442914</v>
+        <v>0.2335027157442915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069159</v>
+        <v>0.3364439424069162</v>
       </c>
     </row>
     <row r="5">
@@ -2426,10 +2426,10 @@
         <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734026513921177</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054277e-06</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387295</v>
+        <v>0.03527526670387308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.191688294691954</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.853994545471355</v>
+        <v>0.8539945454713548</v>
       </c>
     </row>
     <row r="7">
@@ -2458,10 +2458,10 @@
         <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133382</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125516</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2474,10 +2474,10 @@
         <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982443</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432464</v>
+        <v>0.5954095400432469</v>
       </c>
     </row>
     <row r="9">
@@ -2490,10 +2490,10 @@
         <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409136</v>
+        <v>0.1695280942409139</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342701e-07</v>
+        <v>2.539495077342821e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04456520772617086</v>
+        <v>-0.0445652077261707</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604021031716313</v>
+        <v>0.260402103171632</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517834</v>
+        <v>0.8641137091517843</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798149</v>
+        <v>-0.2737623724798146</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465057</v>
+        <v>0.2787881385465067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3261132423877617</v>
+        <v>0.326113242387764</v>
       </c>
     </row>
     <row r="12">
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118127</v>
+        <v>0.08100487957118148</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097166</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
         <v>0.7550514391424692</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461736</v>
+        <v>0.03917827337461754</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743769</v>
+        <v>0.2572958805743774</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123745</v>
+        <v>0.8789745077123743</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307947</v>
+        <v>-0.05296103812307935</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588713</v>
+        <v>0.2610089865588724</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375523</v>
+        <v>0.8392062624375534</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534159</v>
+        <v>0.1181322726534161</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577177</v>
+        <v>0.2572294350577187</v>
       </c>
       <c r="D15" t="n">
-        <v>0.646055612898408</v>
+        <v>0.6460556128984086</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379581</v>
+        <v>-0.004000986240379481</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311186</v>
+        <v>0.2383903410311192</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655129</v>
+        <v>0.9866094604655132</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395304</v>
+        <v>0.1057185310395306</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421748</v>
+        <v>0.2543340222421759</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6776529122567303</v>
+        <v>0.677652912256731</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733256</v>
+        <v>-0.1377694895733254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313626</v>
+        <v>0.2636874203313636</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546261</v>
+        <v>0.6013412201546282</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223238</v>
+        <v>-0.02557154094223237</v>
       </c>
       <c r="C19" t="n">
-        <v>0.252759790153811</v>
+        <v>0.2527597901538116</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966675</v>
+        <v>0.9194160355966677</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376427</v>
+        <v>-0.07344622569376411</v>
       </c>
       <c r="C20" t="n">
-        <v>0.267457860954101</v>
+        <v>0.2674578609541021</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222772</v>
+        <v>0.7836169672222787</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305059</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244289653245072</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719846</v>
+        <v>0.3983578134719854</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362026</v>
+        <v>-0.1704634573362028</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696748454965904</v>
+        <v>0.269674845496591</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806361</v>
+        <v>0.5273167196806365</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334757</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.287067218044571</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08105838975171785</v>
+        <v>0.0810583897517186</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074267</v>
+        <v>0.9366864721074268</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923891e-10</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2746,10 +2746,10 @@
         <v>-0.5776106069409677</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421807</v>
+        <v>0.1143619392421806</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103943e-07</v>
+        <v>4.401383208103854e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.237316144844174</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377478</v>
+        <v>0.1503781926377481</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757813</v>
+        <v>0.1145360411757815</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998651</v>
+        <v>-0.04350476117998643</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386412</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400213</v>
+        <v>0.7872365295400221</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975732</v>
+        <v>-0.07514354096975739</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223567</v>
+        <v>0.1613683918223571</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120151</v>
+        <v>0.6414556246120158</v>
       </c>
     </row>
     <row r="29">
@@ -2807,29 +2807,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742097</v>
+        <v>0.09749293462742094</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290165</v>
+        <v>0.1543265796290169</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510008</v>
+        <v>0.5275624553510021</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002418133412192873</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007135781003458546</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7347043603418277</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
     <row r="31">
@@ -2839,45 +2839,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962195</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992455039</v>
+        <v>0.008304876992454899</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341576</v>
+        <v>0.5461741835341518</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004129656026475419</v>
+        <v>-0.002418133412192865</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02222260881033174</v>
+        <v>0.007135781003458533</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8525770672961279</v>
+        <v>0.7347043603418282</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2280638724458785</v>
+        <v>-0.004129656026475429</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.02222260881033176</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04668969945129923</v>
+        <v>0.8525770672961277</v>
       </c>
     </row>
     <row r="34">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474495</v>
+        <v>0.006335499136474494</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197181</v>
+        <v>0.006871422968197173</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666435</v>
+        <v>0.3565249957666431</v>
       </c>
     </row>
   </sheetData>
